--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20211.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -76,19 +76,10 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
     <t>CORONA</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>VICTOR HUGO</t>
   </si>
   <si>
     <t>MARIA FERNANDA</t>
@@ -492,19 +483,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>77.42</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -518,10 +509,10 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3">
         <v>12</v>
@@ -530,7 +521,7 @@
         <v>57.14</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -544,10 +535,10 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <v>31</v>
@@ -556,7 +547,7 @@
         <v>88.56999999999999</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -570,10 +561,10 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5">
         <v>14</v>
@@ -582,7 +573,7 @@
         <v>66.67</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -635,16 +626,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
         <v>24</v>
       </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>77.42</v>
+      </c>
+      <c r="H2">
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -658,16 +652,19 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
         <v>12</v>
       </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>57.14</v>
+      </c>
+      <c r="H3">
+        <v>7.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -681,16 +678,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E4">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>77.14</v>
+      </c>
+      <c r="H4">
+        <v>8.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -704,16 +704,19 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E5">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>57.14</v>
+      </c>
+      <c r="H5">
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -766,19 +769,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>77.42</v>
+        <v>83.87</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -792,19 +795,19 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>57.14</v>
+        <v>66.67</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -818,19 +821,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>88.56999999999999</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -844,19 +847,19 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G5">
-        <v>66.67</v>
+        <v>76.19</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -866,7 +869,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -898,48 +901,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920396</v>
+        <v>20330051920119</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
         <v>21</v>
       </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920119</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20211.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20211.xlsx
@@ -535,16 +535,16 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>88.56999999999999</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="H4">
         <v>8.199999999999999</v>
@@ -652,19 +652,19 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3">
-        <v>57.14</v>
+        <v>61.9</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -678,16 +678,16 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>77.14</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H4">
         <v>8.4</v>
@@ -704,19 +704,19 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>57.14</v>
+        <v>61.9</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -807,7 +807,7 @@
         <v>66.67</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -821,16 +821,16 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>91.43000000000001</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H4">
         <v>8.5</v>
@@ -859,7 +859,7 @@
         <v>76.19</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -919,7 +919,7 @@
         <v>11</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20211.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20211.xlsx
@@ -483,19 +483,19 @@
         <v>31</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>5</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
       <c r="F2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>80.65000000000001</v>
+        <v>83.87</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -509,10 +509,10 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F3">
         <v>12</v>
@@ -521,7 +521,7 @@
         <v>57.14</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -561,19 +561,19 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G5">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -626,19 +626,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>77.42</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -652,19 +652,19 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>61.9</v>
+        <v>66.67</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -678,19 +678,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>85.70999999999999</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -704,19 +704,19 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G5">
-        <v>61.9</v>
+        <v>80.95</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -769,19 +769,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>83.87</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -795,10 +795,10 @@
         <v>21</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>7</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
       </c>
       <c r="F3">
         <v>14</v>
@@ -807,7 +807,7 @@
         <v>66.67</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -833,7 +833,7 @@
         <v>94.29000000000001</v>
       </c>
       <c r="H4">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -847,19 +847,19 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G5">
-        <v>76.19</v>
+        <v>80.95</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20211.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="64">
   <si>
     <t>Mat</t>
   </si>
@@ -76,13 +76,139 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CEREZO</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>BENITEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>OCAÑA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>CORONA</t>
   </si>
   <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>OLIVERA</t>
+  </si>
+  <si>
+    <t>DAMIEN</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>DULCE FERNANDA</t>
+  </si>
+  <si>
+    <t>SILVIA ANGELICA</t>
+  </si>
+  <si>
+    <t>KITZIA YAMILET</t>
+  </si>
+  <si>
+    <t>SHADAI COSTANTIN</t>
+  </si>
+  <si>
+    <t>CRISTHIAN</t>
+  </si>
+  <si>
+    <t>VICTOR MANUEL</t>
+  </si>
+  <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>MARCO JOSAFAT</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>IRVING</t>
+  </si>
+  <si>
+    <t>OZIEL</t>
+  </si>
+  <si>
+    <t>DANIEL ELEAZAR</t>
+  </si>
+  <si>
     <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>SURISADAY</t>
   </si>
 </sst>
 </file>
@@ -781,7 +907,7 @@
         <v>80.65000000000001</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -798,13 +924,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G3">
-        <v>66.67</v>
+        <v>76.19</v>
       </c>
       <c r="H3">
         <v>7.1</v>
@@ -833,7 +959,7 @@
         <v>94.29000000000001</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -850,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G5">
-        <v>80.95</v>
+        <v>76.19</v>
       </c>
       <c r="H5">
         <v>7</v>
@@ -869,7 +995,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -901,24 +1027,369 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920119</v>
+        <v>20330051920193</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>20330051920392</v>
+      </c>
+      <c r="B3" t="s">
         <v>20</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>20330051920194</v>
+      </c>
+      <c r="B4" t="s">
         <v>21</v>
       </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="C4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>20330051920203</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920204</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920207</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>20330051920261</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920267</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920278</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>20330051920281</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>20330051920397</v>
+      </c>
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>20330051920328</v>
+      </c>
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>20330051920330</v>
+      </c>
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>20330051920274</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>20330051920119</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
         <v>11</v>
       </c>
-      <c r="G2">
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>20330051920321</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17">
         <v>1</v>
       </c>
     </row>
